--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="370">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -555,7 +558,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner)
 </t>
   </si>
   <si>
@@ -568,10 +571,128 @@
     <t>.player</t>
   </si>
   <si>
+    <t>PractitionerRole.practitioner.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>PractitionerRole.practitioner.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.practitioner.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>PractitionerRole.practitioner.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>PractitionerRole.practitioner.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>PractitionerRole.practitioner.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-organization)
 </t>
   </si>
   <si>
@@ -582,6 +703,24 @@
   </si>
   <si>
     <t>.scoper</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization.reference</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization.type</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization.identifier</t>
+  </si>
+  <si>
+    <t>PractitionerRole.organization.display</t>
   </si>
   <si>
     <t>PractitionerRole.code</t>
@@ -603,9 +742,6 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>https://termgit.elga.gv.at/ValueSet/hl7-at-practitionerrole</t>
   </si>
   <si>
@@ -613,6 +749,181 @@
   </si>
   <si>
     <t>.code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -721,29 +1032,7 @@
     <t>PractitionerRole.availableTime.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime.modifierExtension</t>
@@ -1004,6 +1293,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1185,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.26953125" customWidth="true" bestFit="true"/>
@@ -1198,7 +1502,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.19140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.40625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1212,11 +1516,11 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="37.08203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="40.26953125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1351,7 +1655,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1463,7 +1767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1577,7 +1881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1689,7 +1993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1803,7 +2107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -1917,7 +2221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2031,7 +2335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2145,7 +2449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2259,7 +2563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2375,7 +2679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2489,7 +2793,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>154</v>
       </c>
@@ -2607,7 +2911,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>164</v>
       </c>
@@ -2740,7 +3044,7 @@
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -2833,7 +3137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>178</v>
       </c>
@@ -2858,7 +3162,7 @@
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>179</v>
@@ -2918,7 +3222,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2930,13 +3234,13 @@
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -2945,16 +3249,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2970,23 +3274,21 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
@@ -3010,29 +3312,31 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="Y16" s="2"/>
-      <c r="Z16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3044,16 +3348,16 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -3061,10 +3365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3075,10 +3379,10 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -3087,15 +3391,17 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3120,13 +3426,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3144,39 +3450,39 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>131</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3187,7 +3493,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3199,15 +3505,17 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3232,13 +3540,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3256,13 +3564,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -3274,21 +3582,21 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3299,7 +3607,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3308,18 +3616,20 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3374,7 +3684,7 @@
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
@@ -3383,10 +3693,10 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -3395,12 +3705,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3411,7 +3721,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3423,18 +3733,18 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3488,7 +3798,7 @@
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -3500,7 +3810,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -3511,10 +3821,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3525,29 +3835,27 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3596,13 +3904,13 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
@@ -3614,7 +3922,7 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -3623,12 +3931,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3651,13 +3959,13 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3708,7 +4016,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3726,7 +4034,7 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -3735,12 +4043,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3769,7 +4077,7 @@
         <v>135</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>137</v>
@@ -3810,19 +4118,19 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3840,7 +4148,7 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -3851,46 +4159,44 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3938,19 +4244,19 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
@@ -3965,12 +4271,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3981,7 +4287,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -3990,18 +4296,20 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4026,13 +4334,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4050,13 +4358,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4068,7 +4376,7 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4077,12 +4385,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4102,18 +4410,20 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4162,7 +4472,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4180,21 +4490,21 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4214,19 +4524,19 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>250</v>
+        <v>179</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4276,7 +4586,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4294,7 +4604,7 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4305,10 +4615,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4316,33 +4626,35 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4366,13 +4678,11 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4390,13 +4700,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -4405,24 +4715,24 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4433,7 +4743,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4445,13 +4755,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4502,25 +4812,25 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4529,23 +4839,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4557,15 +4867,17 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>227</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>228</v>
+        <v>135</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4602,37 +4914,37 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -4643,44 +4955,46 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>238</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4728,7 +5042,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4740,13 +5054,13 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -4755,48 +5069,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -4844,25 +5154,25 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
@@ -4871,23 +5181,23 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -4899,15 +5209,17 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>227</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -4944,37 +5256,37 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>263</v>
+        <v>189</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -4985,10 +5297,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4996,31 +5308,35 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5068,7 +5384,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5083,10 +5399,10 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5097,10 +5413,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5114,24 +5430,26 @@
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5180,7 +5498,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5195,10 +5513,10 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5209,10 +5527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5220,32 +5538,32 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>273</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5294,13 +5612,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -5309,19 +5627,2645 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN59">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI58">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2584" uniqueCount="424">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -294,7 +294,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -326,14 +326,191 @@
 </t>
   </si>
   <si>
-    <t>PractitionerRole.implicitRules</t>
+    <t>PractitionerRole.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>PractitionerRole.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -399,6 +576,59 @@
     <t>Act.text?</t>
   </si>
   <si>
+    <t>PractitionerRole.text.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.text.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.text.status</t>
+  </si>
+  <si>
+    <t>Siehe Notes - "Regeln für den Inhalt der narrativen Teile in den Notes".</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>PractitionerRole.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
+  </si>
+  <si>
     <t>PractitionerRole.contained</t>
   </si>
   <si>
@@ -422,47 +652,22 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>PractitionerRole.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>PractitionerRole.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -574,39 +779,7 @@
     <t>PractitionerRole.practitioner.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>PractitionerRole.practitioner.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>PractitionerRole.practitioner.reference</t>
@@ -639,9 +812,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -760,10 +930,6 @@
     <t>PractitionerRole.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Code defined by a terminology system</t>
   </si>
   <si>
@@ -1049,6 +1215,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
@@ -1059,9 +1228,6 @@
   </si>
   <si>
     <t>Indicates which days of the week are available between the start and end Times.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>The days of the week.</t>
@@ -1489,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN59"/>
+  <dimension ref="A1:AN71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.26953125" customWidth="true" bestFit="true"/>
@@ -1516,7 +1682,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1767,7 +1933,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1780,13 +1946,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -1881,7 +2047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1900,7 +2066,7 @@
         <v>88</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -2015,10 +2181,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>102</v>
@@ -2029,9 +2195,7 @@
       <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2080,7 +2244,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2092,13 +2256,13 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>21</v>
@@ -2116,14 +2280,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2135,16 +2299,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2170,49 +2334,49 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>21</v>
@@ -2223,14 +2387,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2246,10 +2410,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>119</v>
@@ -2326,7 +2490,7 @@
         <v>21</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>21</v>
@@ -2337,21 +2501,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -2360,19 +2524,19 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2422,25 +2586,25 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
@@ -2451,21 +2615,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2474,19 +2638,19 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2536,25 +2700,25 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>21</v>
@@ -2563,48 +2727,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2652,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2664,13 +2826,13 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>21</v>
@@ -2681,10 +2843,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2707,18 +2869,18 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2742,13 +2904,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -2766,7 +2928,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2781,24 +2943,24 @@
         <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2809,7 +2971,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
@@ -2821,76 +2983,72 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="P12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="R12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>154</v>
-      </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
@@ -2899,24 +3057,24 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2927,30 +3085,30 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2998,7 +3156,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3013,24 +3171,24 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3044,24 +3202,26 @@
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3086,13 +3246,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3110,7 +3270,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3128,7 +3288,7 @@
         <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -3137,16 +3297,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3156,7 +3316,7 @@
         <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3165,15 +3325,17 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3222,7 +3384,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3234,13 +3396,13 @@
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3251,21 +3413,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3277,17 +3439,15 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3324,37 +3484,37 @@
         <v>21</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3363,44 +3523,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>193</v>
+        <v>112</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3438,37 +3598,37 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3477,12 +3637,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3490,32 +3650,30 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3540,13 +3698,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3564,10 +3722,10 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>88</v>
@@ -3582,7 +3740,7 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>21</v>
@@ -3591,12 +3749,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3604,31 +3762,31 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3678,10 +3836,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -3690,13 +3848,13 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -3707,21 +3865,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3730,19 +3888,19 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3792,25 +3950,25 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -3819,43 +3977,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>110</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3904,25 +4064,25 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -3933,10 +4093,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3947,25 +4107,25 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4016,25 +4176,25 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -4045,14 +4205,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4068,21 +4228,21 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4118,19 +4278,19 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4142,27 +4302,27 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4176,7 +4336,7 @@
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -4185,22 +4345,26 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4244,7 +4408,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4253,30 +4417,30 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>131</v>
+        <v>228</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>21</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4299,18 +4463,18 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4334,13 +4498,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4358,7 +4522,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4373,24 +4537,24 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4404,7 +4568,7 @@
         <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4413,17 +4577,15 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4472,7 +4634,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4490,7 +4652,7 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4501,10 +4663,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4524,20 +4686,18 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4586,7 +4746,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4598,13 +4758,13 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>21</v>
@@ -4613,48 +4773,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>229</v>
+        <v>111</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4678,29 +4836,31 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>226</v>
+        <v>116</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4712,27 +4872,27 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>234</v>
+        <v>106</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4746,24 +4906,26 @@
         <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4812,7 +4974,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4821,16 +4983,16 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4841,21 +5003,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4864,19 +5026,19 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>135</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4902,50 +5064,50 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>183</v>
-      </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
@@ -4953,12 +5115,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4966,13 +5128,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -4981,20 +5143,18 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5042,13 +5202,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5057,10 +5217,10 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -5071,10 +5231,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5094,18 +5254,20 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5154,7 +5316,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>182</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5166,13 +5328,13 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
@@ -5181,45 +5343,43 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>271</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>135</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5256,37 +5416,37 @@
         <v>21</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>189</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5295,12 +5455,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5308,35 +5468,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5384,7 +5540,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>253</v>
+        <v>105</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5396,13 +5552,13 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>255</v>
+        <v>106</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5411,44 +5567,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>257</v>
+        <v>110</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>258</v>
+        <v>111</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>259</v>
+        <v>112</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5486,37 +5642,37 @@
         <v>21</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>260</v>
+        <v>116</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>262</v>
+        <v>106</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5527,10 +5683,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5538,7 +5694,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>88</v>
@@ -5553,18 +5709,18 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5612,7 +5768,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5621,16 +5777,16 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5639,12 +5795,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5658,7 +5814,7 @@
         <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5667,18 +5823,18 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -5702,13 +5858,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -5726,7 +5882,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5741,10 +5897,10 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5755,10 +5911,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5781,20 +5937,18 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -5842,7 +5996,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5857,10 +6011,10 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -5871,10 +6025,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5885,7 +6039,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -5897,20 +6051,18 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -5958,7 +6110,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5973,10 +6125,10 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -5985,12 +6137,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5998,13 +6150,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6013,16 +6165,20 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6046,13 +6202,11 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6070,7 +6224,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6085,13 +6239,13 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>300</v>
+        <v>237</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6099,10 +6253,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6113,7 +6267,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6122,16 +6276,16 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>302</v>
+        <v>102</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>103</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>304</v>
+        <v>104</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6182,43 +6336,43 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>301</v>
+        <v>105</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>305</v>
+        <v>106</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6237,15 +6391,17 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>309</v>
+        <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>310</v>
+        <v>110</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6282,19 +6438,19 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>308</v>
+        <v>116</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6306,13 +6462,13 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>313</v>
+        <v>106</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6321,12 +6477,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6334,13 +6490,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6349,17 +6505,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>315</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6408,7 +6566,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6423,10 +6581,10 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6437,10 +6595,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6451,7 +6609,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6463,17 +6621,15 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>321</v>
+        <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>322</v>
+        <v>103</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6522,25 +6678,25 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>105</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>325</v>
+        <v>106</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6551,21 +6707,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6577,15 +6733,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6622,37 +6780,37 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>183</v>
+        <v>106</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6661,46 +6819,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>185</v>
+        <v>304</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6748,25 +6908,25 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>307</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>183</v>
+        <v>309</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -6775,48 +6935,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -6864,25 +7022,25 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>131</v>
+        <v>316</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
@@ -6891,12 +7049,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6904,31 +7062,33 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -6952,13 +7112,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -6976,13 +7136,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -6991,10 +7151,10 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
@@ -7003,12 +7163,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7022,25 +7182,27 @@
         <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7088,7 +7250,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7103,10 +7265,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
@@ -7117,10 +7279,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7140,21 +7302,23 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>343</v>
+        <v>221</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7202,7 +7366,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7217,10 +7381,10 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
@@ -7231,10 +7395,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7245,7 +7409,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7254,21 +7418,23 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O51" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -7316,7 +7482,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7331,10 +7497,10 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7345,10 +7511,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7368,16 +7534,16 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7404,13 +7570,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7428,7 +7594,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7443,13 +7609,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -7457,10 +7623,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7471,7 +7637,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7480,16 +7646,16 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>179</v>
+        <v>356</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>180</v>
+        <v>357</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>181</v>
+        <v>358</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7540,43 +7706,43 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>182</v>
+        <v>355</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>183</v>
+        <v>359</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7595,17 +7761,15 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>363</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>135</v>
+        <v>364</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -7654,7 +7818,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>189</v>
+        <v>362</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7666,13 +7830,13 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>21</v>
+        <v>366</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>183</v>
+        <v>367</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -7683,14 +7847,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7703,25 +7867,23 @@
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>369</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>143</v>
+        <v>372</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7770,7 +7932,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7782,13 +7944,13 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>131</v>
+        <v>373</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -7799,10 +7961,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7810,10 +7972,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -7825,15 +7987,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>179</v>
+        <v>375</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -7882,13 +8046,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -7900,7 +8064,7 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>183</v>
+        <v>379</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
@@ -7911,10 +8075,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7937,13 +8101,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>360</v>
+        <v>103</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>361</v>
+        <v>104</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7994,7 +8158,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>359</v>
+        <v>105</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8006,13 +8170,13 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>325</v>
+        <v>106</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -8023,21 +8187,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8049,15 +8213,17 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>363</v>
+        <v>110</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8106,25 +8272,25 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>362</v>
+        <v>116</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>325</v>
+        <v>106</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -8135,14 +8301,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8155,23 +8321,25 @@
         <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>366</v>
+        <v>109</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8220,7 +8388,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8232,23 +8400,1379 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AK60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN59">
+  <autoFilter ref="A1:AN71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8258,7 +9782,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
